--- a/master-exports/master_kategori_bahan.xlsx
+++ b/master-exports/master_kategori_bahan.xlsx
@@ -7,10 +7,10 @@
     <workbookView activeTab="0" autoFilterDateGrouping="true" firstSheet="0" minimized="false" showHorizontalScroll="true" showSheetTabs="true" showVerticalScroll="true" tabRatio="600" visibility="visible"/>
   </bookViews>
   <sheets>
-    <sheet name="Worksheet" sheetId="1" r:id="rId4"/>
+    <sheet name="Kategori Bahan" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="999999" calcMode="auto" calcCompleted="0" fullCalcOnLoad="1" forceFullCalc="1"/>
+  <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
@@ -83,16 +83,22 @@
       <strike val="0"/>
       <u val="none"/>
       <sz val="11"/>
-      <color rgb="FF000000"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1e40af"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -109,7 +115,9 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
-    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="2" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -411,6 +419,11 @@
   </sheetPr>
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col min="1" max="1" width="13.997" bestFit="true" customWidth="true" style="0"/>
+    <col min="2" max="2" width="13.997" bestFit="true" customWidth="true" style="0"/>
+    <col min="3" max="3" width="15.139" bestFit="true" customWidth="true" style="0"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
